--- a/ארגון חתונה - עומר ונועה.xlsx
+++ b/ארגון חתונה - עומר ונועה.xlsx
@@ -403,7 +403,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L19"/>
+  <dimension ref="A1:M19"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1" hidden="true"/>
     <col min="2" max="2" width="25.83203125" customWidth="1"/>
@@ -413,10 +413,11 @@
     <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="8.83203125" customWidth="1"/>
     <col min="8" max="8" width="13.83203125" customWidth="1"/>
-    <col min="9" max="9" width="8.83203125" customWidth="1"/>
-    <col min="10" max="10" width="9.83203125" customWidth="1"/>
-    <col min="11" max="11" width="8.83203125" customWidth="1"/>
-    <col min="12" max="12" width="19.83203125" customWidth="1"/>
+    <col min="9" max="9" width="14.83203125" customWidth="1"/>
+    <col min="10" max="10" width="8.83203125" customWidth="1"/>
+    <col min="11" max="11" width="9.83203125" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" customWidth="1"/>
+    <col min="13" max="13" width="19.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,21 +446,24 @@
         <v>אישור הגעה</v>
       </c>
       <c r="I1" t="str">
+        <v>סבירות הגעה</v>
+      </c>
+      <c r="J1" t="str">
         <v>הגיע</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>מתנה ₪</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>שולחן</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>הערות</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>15jixem</v>
+        <v>4kpppss</v>
       </c>
       <c r="B2" t="str">
         <v>משפחת לוי - דוד ורונית</v>
@@ -483,21 +487,24 @@
         <v>אישר</v>
       </c>
       <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="K2" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2">
+        <v>0</v>
       </c>
       <c r="L2" t="str">
+        <v/>
+      </c>
+      <c r="M2" t="str">
         <v>הורים של עומר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>uhpvc3n</v>
+        <v>ed532lh</v>
       </c>
       <c r="B3" t="str">
         <v>יעל לוי</v>
@@ -521,21 +528,24 @@
         <v>אישר</v>
       </c>
       <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3">
+        <v>0</v>
       </c>
       <c r="L3" t="str">
+        <v/>
+      </c>
+      <c r="M3" t="str">
         <v>אחות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>e57xhdm</v>
+        <v>1froxkd</v>
       </c>
       <c r="B4" t="str">
         <v>סבתא מרים</v>
@@ -559,21 +569,24 @@
         <v>אישר</v>
       </c>
       <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4">
-        <v>0</v>
-      </c>
-      <c r="K4" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4">
+        <v>0</v>
       </c>
       <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v>להושיב קרוב לבמה</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>g9g3xe7</v>
+        <v>t3a0ka8</v>
       </c>
       <c r="B5" t="str">
         <v>משפחת ברקוביץ</v>
@@ -597,21 +610,24 @@
         <v>טרם</v>
       </c>
       <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5" t="str">
-        <v/>
+        <v>בינונית</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5">
+        <v>0</v>
       </c>
       <c r="L5" t="str">
+        <v/>
+      </c>
+      <c r="M5" t="str">
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>kye3f0q</v>
+        <v>oxataur</v>
       </c>
       <c r="B6" t="str">
         <v>אורי כהן</v>
@@ -635,21 +651,24 @@
         <v>אישר</v>
       </c>
       <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6">
-        <v>0</v>
-      </c>
-      <c r="K6" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6">
+        <v>0</v>
       </c>
       <c r="L6" t="str">
+        <v/>
+      </c>
+      <c r="M6" t="str">
         <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>suwimmg</v>
+        <v>36fgchm</v>
       </c>
       <c r="B7" t="str">
         <v>רון פרץ</v>
@@ -673,21 +692,24 @@
         <v>טרם</v>
       </c>
       <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7">
-        <v>0</v>
-      </c>
-      <c r="K7" t="str">
-        <v/>
+        <v>בינונית</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7">
+        <v>0</v>
       </c>
       <c r="L7" t="str">
+        <v/>
+      </c>
+      <c r="M7" t="str">
         <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>s6v665k</v>
+        <v>98li5a5</v>
       </c>
       <c r="B8" t="str">
         <v>נדב שגיא</v>
@@ -711,21 +733,24 @@
         <v>אישר</v>
       </c>
       <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8">
+        <v>0</v>
       </c>
       <c r="L8" t="str">
+        <v/>
+      </c>
+      <c r="M8" t="str">
         <v>מנהל הצוות</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>jf1d45p</v>
+        <v>zwyba01</v>
       </c>
       <c r="B9" t="str">
         <v>שירה אלון</v>
@@ -749,21 +774,24 @@
         <v>טרם</v>
       </c>
       <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9" t="str">
-        <v/>
+        <v>בינונית</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9">
+        <v>0</v>
       </c>
       <c r="L9" t="str">
+        <v/>
+      </c>
+      <c r="M9" t="str">
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>7o5jcps</v>
+        <v>ehdavau</v>
       </c>
       <c r="B10" t="str">
         <v>גיא ומאיה</v>
@@ -787,21 +815,24 @@
         <v>אישר</v>
       </c>
       <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10">
+        <v>0</v>
       </c>
       <c r="L10" t="str">
+        <v/>
+      </c>
+      <c r="M10" t="str">
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>fovo9kg</v>
+        <v>46i0akm</v>
       </c>
       <c r="B11" t="str">
         <v>משפחת אזולאי</v>
@@ -825,21 +856,24 @@
         <v>אישר</v>
       </c>
       <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11">
+        <v>0</v>
       </c>
       <c r="L11" t="str">
+        <v/>
+      </c>
+      <c r="M11" t="str">
         <v>הורים של נועה</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>rzio8px</v>
+        <v>e3bi6rn</v>
       </c>
       <c r="B12" t="str">
         <v>תמר אזולאי</v>
@@ -863,21 +897,24 @@
         <v>אישר</v>
       </c>
       <c r="I12" t="str">
-        <v/>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12">
+        <v>0</v>
       </c>
       <c r="L12" t="str">
+        <v/>
+      </c>
+      <c r="M12" t="str">
         <v>אחות + עדה</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>e56c1b3</v>
+        <v>tfe1o7o</v>
       </c>
       <c r="B13" t="str">
         <v>דודה אילנה</v>
@@ -901,21 +938,24 @@
         <v>טרם</v>
       </c>
       <c r="I13" t="str">
-        <v/>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" t="str">
-        <v/>
+        <v>בינונית</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13">
+        <v>0</v>
       </c>
       <c r="L13" t="str">
+        <v/>
+      </c>
+      <c r="M13" t="str">
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>c3v03ov</v>
+        <v>k3ap3zc</v>
       </c>
       <c r="B14" t="str">
         <v>נועם ברק</v>
@@ -939,21 +979,24 @@
         <v>אישר</v>
       </c>
       <c r="I14" t="str">
-        <v/>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14">
+        <v>0</v>
       </c>
       <c r="L14" t="str">
+        <v/>
+      </c>
+      <c r="M14" t="str">
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>f0tl7c4</v>
+        <v>6a4s8gf</v>
       </c>
       <c r="B15" t="str">
         <v>הילה מזרחי</v>
@@ -977,21 +1020,24 @@
         <v>אישר</v>
       </c>
       <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15">
+        <v>0</v>
       </c>
       <c r="L15" t="str">
+        <v/>
+      </c>
+      <c r="M15" t="str">
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>f1aea8q</v>
+        <v>ohcowog</v>
       </c>
       <c r="B16" t="str">
         <v>ליאור ואפרת</v>
@@ -1015,21 +1061,24 @@
         <v>טרם</v>
       </c>
       <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" t="str">
-        <v/>
+        <v>בינונית</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16">
+        <v>0</v>
       </c>
       <c r="L16" t="str">
+        <v/>
+      </c>
+      <c r="M16" t="str">
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>d7tbzgw</v>
+        <v>hucij98</v>
       </c>
       <c r="B17" t="str">
         <v>דנה שטרן</v>
@@ -1053,21 +1102,24 @@
         <v>לא מגיע</v>
       </c>
       <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17" t="str">
-        <v/>
+        <v>נמוכה</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17">
+        <v>0</v>
       </c>
       <c r="L17" t="str">
+        <v/>
+      </c>
+      <c r="M17" t="str">
         <v>בחו״ל</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>a8fh8sr</v>
+        <v>35kmkg3</v>
       </c>
       <c r="B18" t="str">
         <v>מיכל רוזן</v>
@@ -1091,21 +1143,24 @@
         <v>אישר</v>
       </c>
       <c r="I18" t="str">
-        <v/>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18" t="str">
-        <v/>
+        <v>גבוהה</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18">
+        <v>0</v>
       </c>
       <c r="L18" t="str">
+        <v/>
+      </c>
+      <c r="M18" t="str">
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>bnij2ma</v>
+        <v>s0mv35t</v>
       </c>
       <c r="B19" t="str">
         <v>משפחת שוורץ</v>
@@ -1129,21 +1184,24 @@
         <v>טרם</v>
       </c>
       <c r="I19" t="str">
-        <v/>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19" t="str">
-        <v/>
+        <v>בינונית</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19">
+        <v>0</v>
       </c>
       <c r="L19" t="str">
+        <v/>
+      </c>
+      <c r="M19" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L19"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M19"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -1182,7 +1240,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>p0bq5z1</v>
+        <v>zs3qht4</v>
       </c>
       <c r="B2" t="str">
         <v>שולחן 1</v>
@@ -1202,7 +1260,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>l5ghqiq</v>
+        <v>3uf9yr8</v>
       </c>
       <c r="B3" t="str">
         <v>שולחן 2</v>
@@ -1222,7 +1280,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>syfnc7x</v>
+        <v>whzjlsp</v>
       </c>
       <c r="B4" t="str">
         <v>שולחן 3</v>
@@ -1242,7 +1300,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ny6bge3</v>
+        <v>fnvmco6</v>
       </c>
       <c r="B5" t="str">
         <v>שולחן אבירים</v>
@@ -1317,7 +1375,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>f0eqcav</v>
+        <v>0n849ca</v>
       </c>
       <c r="B2" t="str">
         <v>די ג׳יי</v>
@@ -1349,7 +1407,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>rkeitt9</v>
+        <v>udkbfnd</v>
       </c>
       <c r="B3" t="str">
         <v>צלם סטילס</v>
@@ -1381,7 +1439,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>rqsnni3</v>
+        <v>s3dzsov</v>
       </c>
       <c r="B4" t="str">
         <v>איפור ושיער</v>
@@ -1413,7 +1471,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>bkk0yga</v>
+        <v>nsd0plj</v>
       </c>
       <c r="B5" t="str">
         <v>עיצוב ופרחים</v>
@@ -1445,7 +1503,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>bfhgu1j</v>
+        <v>sa4a57d</v>
       </c>
       <c r="B6" t="str">
         <v>רב</v>
@@ -1528,7 +1586,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>5lfj9lx</v>
+        <v>agkdgxe</v>
       </c>
       <c r="B2" t="str">
         <v>בית רבן</v>
@@ -1557,7 +1615,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ivyvpul</v>
+        <v>wpg9ecy</v>
       </c>
       <c r="B3" t="str">
         <v>בית ברל</v>
@@ -1586,7 +1644,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>yuutixz</v>
+        <v>5v1isms</v>
       </c>
       <c r="B4" t="str">
         <v>מחסיה</v>
@@ -1615,7 +1673,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>0p80ylb</v>
+        <v>ju55qr0</v>
       </c>
       <c r="B5" t="str">
         <v>חדרה - צהריים</v>
@@ -1679,7 +1737,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>dpiw434</v>
+        <v>8k6czml</v>
       </c>
       <c r="B2" t="str">
         <v>לסגור אולם ולחתום חוזה</v>
@@ -1696,7 +1754,7 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>ps3kldf</v>
+        <v>0gtn4pi</v>
       </c>
       <c r="B3" t="str">
         <v>לקבוע טעימות</v>
@@ -1713,7 +1771,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>9wqdyjk</v>
+        <v>drghwd8</v>
       </c>
       <c r="B4" t="str">
         <v>לסיים רשימת מוזמנים סופית</v>
@@ -1730,7 +1788,7 @@
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ke4wdry</v>
+        <v>vbxpa7a</v>
       </c>
       <c r="B5" t="str">
         <v>להזמין הזמנות דיגיטליות</v>
@@ -1747,7 +1805,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>kr3j3wd</v>
+        <v>hfmsds5</v>
       </c>
       <c r="B6" t="str">
         <v>מדידות שמלה</v>
@@ -1764,7 +1822,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>rs0lwpl</v>
+        <v>9s09pqk</v>
       </c>
       <c r="B7" t="str">
         <v>חליפה לחתן</v>
@@ -1781,7 +1839,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>2mjbfux</v>
+        <v>sqken7u</v>
       </c>
       <c r="B8" t="str">
         <v>לסגור צלם וידאו</v>
@@ -1798,7 +1856,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>wk6x2br</v>
+        <v>exilojc</v>
       </c>
       <c r="B9" t="str">
         <v>לתאם עם הרב</v>
@@ -1815,7 +1873,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>g1lisom</v>
+        <v>s6wy0l2</v>
       </c>
       <c r="B10" t="str">
         <v>רישום רבנות</v>
